--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-ClaimRef.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-ClaimRef.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T09:28:26+00:00</t>
+    <t>2025-02-06T11:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-ClaimRef.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-ClaimRef.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T11:21:55+00:00</t>
+    <t>2025-02-06T12:00:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-ClaimRef.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-ClaimRef.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T12:00:33+00:00</t>
+    <t>2025-02-10T09:34:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-ClaimRef.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-ClaimRef.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T09:34:03+00:00</t>
+    <t>2025-02-10T11:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,7 +129,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:http://example.org/StructureDefinition/MOPEDAccount#Account</t>
+    <t>element:http://example.org/StructureDefinition/MopedAccount#Account</t>
   </si>
   <si>
     <t>ID</t>
@@ -328,7 +328,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MOPEDClaim)
+    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedLKFRequest)
 </t>
   </si>
   <si>
@@ -666,7 +666,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="59.58203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="64.640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-ClaimRef.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-ClaimRef.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
